--- a/instance/round_robin_schedule.xlsx
+++ b/instance/round_robin_schedule.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,51 +569,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Irwin Sunarto / Brandon Pham</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Zhuoran Cheng / Hancheng Li</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Irwin Sunarto / Brandon Pham</t>
+          <t>Makenna Wong / Meghan Wong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zhuoran Cheng / Hancheng Li</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -623,22 +623,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Makenna Wong / Meghan Wong</t>
+          <t>Haipeng Huang / Charles Yang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Stephen Guan / Midy Tao</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
@@ -648,838 +648,813 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Haipeng Huang / Charles Yang</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephen Guan / Midy Tao</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Reyna Wan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Liu, Junjie Zhou, Yifei Zheng</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu / Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Yantao Fang / Siyang Chang</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Anais Molinaro / Martin Lee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Wenhao Zhang / Yingchao Peng</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Siyuan Chen / Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu, Yuhung Kung</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu / Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Jason Liu</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Gustabo Adolpho Lucas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="A13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Juncheng Tang / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Heng Wu, Aryan Khandekar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Elisa Liu / Reyna Wan</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
+          <t>Yen Zhen Tan / Sirui Jiang</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Elisa Liu, Reyna Wan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yantao Fang / Siyang Chang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Anais Molinaro / Martin Lee</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Irwin Sunarto / Brandon Pham</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Zhoran Cheng / Hancheng Li</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Juncheng Tang</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh, Haonan Wang, Prathamesh Koranne, Avi Aswal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh, Prathamesh Koranne</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Haonan Wang, Avi Aswal, Juncheng Tang</t>
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ted Mao / Jean Luo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Haipeng Huang / Jiayi Shi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elisa Liu / Reyna Wan</t>
+          <t>Wenhao Zhang / Yingchao Peng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yen Zhen Tan / Sirui Jiang</t>
+          <t>Siyuan Chen / Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Irwin Sunarto / Brandon Pham</t>
+          <t>Yijun Liu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zhoran Cheng / Hancheng Li</t>
+          <t>Makenna Wong</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang / Avi Aswal</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3</v>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar, Heng Wu</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>3</v>
+      <c r="A21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Elisa Liu</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ted Mao / Jean Luo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Haipeng Huang / Jiayi Shi</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Reyna Wan</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Yang Jiao / Bernice Tung</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Reyna Wan</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Makenna Wong</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Reyna Wan</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Yifei Zheng, Meghan Wong, Reyna Wan</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="A24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu / Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang / Avi Aswal</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zain Merchant</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Martin Lee</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Irwin Sunarto / Chelsea Huang</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Shan Zhong / Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hancheng Li / Sirui Jiang</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brandon Pham</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Stephen Guan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Vincent Onggoputra</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang / Avi Aswal</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Juncheng Tang / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Avi Aswal, Haonan Wang</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Haonan Wang / Avi Aswal</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Manmeeth Nagesh, Avi Aswal, Haonan Wang</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Juncheng Tang / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu / Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Juncheng Tang, Yifei Zheng</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Shiyang Chang</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gustabo Adolpho Lucas</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Yang Jiao / Bernice Tung</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Reyna Wan</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Junjie Zhou / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Elisa Liu, Prathamesh Koranne</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang, Avi Aswal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Prathamesh Koranne, Reyna Wan, Meghan Wong</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu, Aryan Khandekar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Zhuoran Cheng / Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Irwin Sunarto / Chelsea Huang</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Shan Zhong / Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Hancheng Li / Sirui Jiang</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Brandon Pham</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Jason Liu, Yuhung Kung</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh, Prathamesh Koranne, Heng Wu, Aryan Khandekar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu, Yuhung Kung</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Yang Jiao / Bernice Tung</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Junjie Zhou / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/instance/round_robin_schedule.xlsx
+++ b/instance/round_robin_schedule.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
+          <t>Winner of R1-M1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Winner of R1-M2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Winner of R2-M1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Winner of R2-M2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yang Jiao / Bernice Tung</t>
+          <t>Makenna Wong</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Junjie Zhou / Elisa Liu</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ryoto Leegomonchai</t>
+          <t>Winner of R1-M3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Winner of R1-M4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -569,16 +569,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Irwin Sunarto / Brandon Pham</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zhuoran Cheng / Hancheng Li</t>
+          <t>Prathamesh Koranne / Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -588,32 +588,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Makenna Wong / Meghan Wong</t>
+          <t>Zhuoran Cheng / Hancheng Li</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -623,22 +623,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haipeng Huang / Charles Yang</t>
+          <t>Yifei Zheng / Reyna Wan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephen Guan / Midy Tao</t>
+          <t>Yang Jiao / Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -648,642 +648,632 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Haipeng Huang / charles yang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Junjie Zhou / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Haonan Wang / Avi Aswal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar / Heng Wu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cynthia Liu / Hanna Yun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yen Zhen  Tan / Sirui Jiang</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Martin Lee / Anais Molinaro</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Shan Zhong / Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Elisa Liu, Junjie Zhou, Yifei Zheng</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Winner of R1-M5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Winner of R1-M6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu, Yuhung Kung</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung, Jason Liu</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Heng Wu, Aryan Khandekar</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Shiyang  CHang</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Elisa Liu / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Yen Zhen Tan / Sirui Jiang</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu / Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Winner of R1-M3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Winner of R1-M4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Meghan  Wong / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Irwin Sunarto / Brandon Pham</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hancheng  Li / Zhuoran Cheng</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cindy Lim / Janice Lee</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sirui Jiang / Yen zhen tan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Elisa Liu, Reyna Wan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Yantao Fang / Siyang Chang</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Anais Molinaro / Martin Lee</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Irwin Sunarto / Brandon Pham</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Zhoran Cheng / Hancheng Li</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ted Mao / Jean Luo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Haipeng Huang / Jiayi Shi</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Wenhao Zhang / Yingchao Peng</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Siyuan Chen / Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Makenna Wong</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar, Heng Wu</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Junjie Zhou / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne, Elisa Liu</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Yang Jiao / Bernice Tung</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Reyna Wan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Reyna Wan</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>XD</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne, Yifei Zheng, Meghan Wong, Reyna Wan</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu / Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang / Avi Aswal</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang, Avi Aswal</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Stephen Guan / Midy Tao</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zain Merchant</t>
+          <t>Wenhao Zhang / Yingchao Peng</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Anais Molinaro / Martin Lee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Haipeng Huang / jiayi shi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zhuoran Cheng / Yen Zhen Tan</t>
+          <t>Winner of R3-M1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irwin Sunarto / Chelsea Huang</t>
+          <t>Winner of R3-M2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shan Zhong / Fanghong Huang</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hancheng Li / Sirui Jiang</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>6</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brandon Pham</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="A30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Fanghong Huang</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
+          <t>BYE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang / Avi Aswal</t>
+          <t>Dominic Pang / Edward Wang</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1293,92 +1283,92 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Avi Aswal, Haonan Wang</t>
+          <t>BYE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Winner of R1-M1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang / Avi Aswal</t>
+          <t>Winner of R1-M2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Manmeeth Nagesh, Avi Aswal, Haonan Wang</t>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Juncheng Tang / Yifei Zheng</t>
+          <t>Winner of R2-M1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu / Yuhung Kung</t>
+          <t>Winner of R2-M2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng</t>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Winner of R1-M3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shiyang Chang</t>
+          <t>Winner of R1-M4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1389,72 +1379,1467 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Yen Zhen  Tan / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gustabo Adolpho Lucas</t>
+          <t>Shiyang  CHang / Yantao Fang</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Elisa Liu / Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Yang Jiao / Bernice Tung</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>XD</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jean Luo / Ted Mao</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Irwin Sunarto / Chelsea huang</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Janice Lee / Cindy Lim</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hanna Yun / Cynthia Liu</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Yingchao Peng / Wenhao Zhang</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Charles  Yang / Haipeng Huang</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winner of R3-M1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Winner of R3-M2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winner of R1-M5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Winner of R1-M6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Yantao Fang / Shiyang Chang</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Yantao Fang, BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Makenna Wong / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winner of R1-M3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Winner of R1-M4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winner of R2-M3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Winner of R2-M4</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
         <v>8</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chelsea Huang / Irwin Sunarto</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ted Mao / Jean luo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Martin Lee</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ryuto Leegomonchai</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Zain Merchant</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>8</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Hancheng  Li / Sirui Jiang</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1, Winner of R2-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>9</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Meghan  Wong / Makenna Wong</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Elisa Liu / Reyna Wan</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>9</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Winner of R1-M3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Winner of R1-M4</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Winner of R2-M3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Winner of R2-M4</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho / Siyuan Chen</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Siyuan Chen / Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Winner of R3-M1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Winner of R3-M2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>10</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Winner of R1-M5</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Winner of R1-M6</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brandon Pham</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>10</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>10</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Haocheng Teng</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Edward  Wang / Dominic Pang</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Winner of R1-M2, Winner of R1-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>11</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Winner of R2-M1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Winner of R2-M2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>11</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Winner of R1-M3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Winner of R1-M4</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Sirui Jiang / Hancheng Li</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Jiayi Shi / Haipeng Huang</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Tsz Ching Chen / Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
